--- a/yt cần validate.xlsx
+++ b/yt cần validate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User c driver data\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User c driver data\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B8E061-8FED-42E8-8961-D687B92A6465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BFA64A-A3AF-4689-B773-C9005852756F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>No</t>
   </si>
@@ -54,55 +54,41 @@
     <t>A</t>
   </si>
   <si>
-    <t>29/7/2026</t>
-  </si>
-  <si>
-    <t>Active Recovery</t>
-  </si>
-  <si>
-    <t>SoftFit: App chuyên về "Ngày nghỉ ngơi" (Active Recovery)
-Văn hóa "tập luyện đến kiệt sức" đang dần bị đào thải. Phụ nữ ngày nay nhận ra tầm quan trọng của việc phục hồi hệ thần kinh.
-Tính năng cốt lõi: Thay vì đếm calo tiêu thụ, app này thưởng điểm cho người dùng khi họ làm các hoạt động phục hồi: Lăn bọt biển (foam rolling), Yoga Nidra, ngâm bồn, ngủ đủ giấc, và các bài tập hít thở.
-Điểm thu hút: Đóng vai trò là một "ứng dụng bổ trợ" (companion app). Ngay cả khi họ đang dùng Peloton để tập nặng, họ vẫn sẽ tải app của bạn để hướng dẫn những ngày nghỉ ngơi.</t>
-  </si>
-  <si>
-    <t>Tính toán chi phí khi đi siêu thị</t>
-  </si>
-  <si>
-    <t>lên kê hoạch ở nhà trước và khi mua chỉ cần tick vào (tích hợp AI giúp gen hình ảnh và giá bán)</t>
-  </si>
-  <si>
-    <t>Bài tập sửa lỗi cột sống do dùng điện thoại và máy tính quá nhiều</t>
-  </si>
-  <si>
-    <t>Bài tập cho mắt</t>
-  </si>
-  <si>
-    <t>(ý tưởng về việc hoàn thành công việc sẽ được thưởng gold, tiền thật)</t>
-  </si>
-  <si>
-    <t>Thêm các bài tập cho phụ nữ sau sinh</t>
-  </si>
-  <si>
-    <t>ý tưởng thêm gì vào tủ lạnh thì nhập vào và sau đó gợi ý món ăn</t>
-  </si>
-  <si>
-    <t>ý tưởng làm app cho người già</t>
-  </si>
-  <si>
-    <t>mỗi ngày 1 bài tập để luyện não, có thể nhắc nhở vận động</t>
-  </si>
-  <si>
-    <t>Xây dựng ứng dụng cho người lớn tuổi</t>
-  </si>
-  <si>
-    <t>nhắc thời tiết ngày mai
-Chỉ có 6–8 nút lớn.
-Chạm vào "Con gái" → gọi ngay., hiển thị đã bao nhiêu ngày chưa gọi cho con gái
-Chạm vào "Bệnh viện" → mở chỉ đường.
-Chạm vào "Thuốc" → mở lời nhắc uống thuốc.
-Chạm vào "Ảnh gia đình" → mở album đã chọn.
-Chạm vào "Video call" → mở FaceTime.</t>
+    <t>ý tưởng app từ bỏ thói quen xấu, kiểu như bỏ thuốc thì cây lớn dần, hay ô nhiễm môi trường giảm đi</t>
+  </si>
+  <si>
+    <t>ý tưởng app pomodoro mà mỗi giây trôi qua có 1 chấm trên màn hình hiện lên đủ màu sắc, kiến cho trải nghiệm 25p thú vị hơn
+                    hoặc ngọn nến sẽ tắt dần mỗi s giảm 1 px (pixel pomodoro)</t>
+  </si>
+  <si>
+    <t>Ý tưởng cai thuốc lá sẽ được mỗi ngày 1 ít oxi, tiền, .... dùng tiền và oxi đó để mua các thứ (ví dụ trồng rừng hay làm gì đó....)</t>
+  </si>
+  <si>
+    <t>ý tưởng fitness tập thể dục thì con chó của bạn sẽ khỏe, mỗi ngày tập 1 tí</t>
+  </si>
+  <si>
+    <t>habit breaking app, bad habit tracker app, habit change app, behavior change app, self improvement app, personal growth app, gamified habit tracker, habit tracker gamification, visual habit progress, progress visualization app, growth based habit app, habit garden app, digital garden app, virtual plant growth app, plant based habit tracker, habit tree app, tree growth habit tracker,</t>
+  </si>
+  <si>
+    <t>pomodoro visual experience, pomodoro animation app, creative pomodoro timer, aesthetic pomodoro app, immersive pomodoro timer, visual timer app, interactive timer app, animated productivity app, gamified pomodoro app, pomodoro gamification, focus timer visualization, focus session animation, relaxing focus app, mindful productivity app, ambient timer app, calming productivity app, sensory timer app, emotional timer app, time visualization app, time passing visualization, creative time tracker, minimal timer UI, beautiful timer app, zen productivity app, focus journey app</t>
+  </si>
+  <si>
+    <t>quit smoking app, smoking cessation app, addiction recovery app, habit recovery app, health transformation app, lifestyle change app, behavior change app, positive habit app, self improvement gamification, wellness gamification, recovery journey app, personal transformation app, habit reward system, healthy habit tracker</t>
+  </si>
+  <si>
+    <t>fitness gamification, fitness game app, workout gamification, exercise motivation app, fitness habit tracker, workout habit app, daily exercise app, fitness journey app, personal fitness progression, health transformation app, gamified fitness tracker, fitness reward system</t>
+  </si>
+  <si>
+    <t>ý tưởng ghi lại giấc mơ theo ngày, mỗi ngày vào sẽ nhập giấc mơ hôm qua là gì (noti thông báo), sau đó giấc mơ tốt sẽ có màu đẹp, mơ xấu thì u ám. Sau nhiều ngày sẽ là 1 bức tranh sống động và gợi ý về sức khỏe</t>
+  </si>
+  <si>
+    <t>ý tưởng ghi lại  tình trạng ngủ mỗi ngày - có ghi nhận qua apple health),noti thông báo), sau đó ngủ tốt thì sẽ có màu đẹp, ngủ kém thì u ám. Sau nhiều ngày sẽ là 1 bức tranh sống động và gợi ý về sức khỏe</t>
+  </si>
+  <si>
+    <t>sleep tracker app, sleep tracking app design, Apple Health sleep app, sleep quality tracker, sleep analysis app, sleep wellness app, sleep improvement app, healthy sleep app, sleep habit tracker, sleep journal app, sleep routine app</t>
+  </si>
+  <si>
+    <t>dream journal app, dream diary app, dream tracker app, dream recording app, dream analysis app, dream interpretation app, sleep journal app, morning journal app, subconscious journal app, dream memory app, lucid dream app</t>
   </si>
 </sst>
 </file>
@@ -173,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -192,6 +178,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -473,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.1796875" bestFit="1" customWidth="1"/>
@@ -481,7 +470,7 @@
     <col min="3" max="3" width="21.36328125" customWidth="1"/>
     <col min="4" max="4" width="9.6328125" style="6" customWidth="1"/>
     <col min="5" max="5" width="55.90625" customWidth="1"/>
-    <col min="6" max="6" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.36328125" customWidth="1"/>
     <col min="7" max="7" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -511,311 +500,125 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="174" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="B2" s="7">
+        <v>46211</v>
+      </c>
+      <c r="C2" s="3"/>
       <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="203" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B3" s="7">
+        <v>46211</v>
+      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="116" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B4" s="7">
+        <v>46211</v>
+      </c>
+      <c r="C4" s="2"/>
       <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B5" s="7">
+        <v>46211</v>
+      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B6" s="7">
+        <v>46211</v>
+      </c>
+      <c r="C6" s="2"/>
       <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B7" s="7">
+        <v>46211</v>
+      </c>
+      <c r="C7" s="2"/>
       <c r="D7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="E7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" ht="116" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
